--- a/etf_holdings/2026-09-17_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-17_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL6"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,200 +539,100 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>00982A_異動類型</t>
+          <t>00993A_異動類型</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>00982A_調整方向</t>
+          <t>00993A_調整方向</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>00982A_股票名稱_昨日</t>
+          <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>00982A_股票名稱_今日</t>
+          <t>00993A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>00982A_權重_昨日</t>
+          <t>00993A_權重_昨日</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>00982A_權重_今日</t>
+          <t>00993A_權重_今日</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>00982A_權重變化</t>
+          <t>00993A_權重變化</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>00982A_股數_昨日</t>
+          <t>00993A_股數_昨日</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>00982A_股數_今日</t>
+          <t>00993A_股數_今日</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>00982A_股數變化</t>
+          <t>00993A_股數變化</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>00403A_異動類型</t>
+          <t>00400A_異動類型</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>00403A_調整方向</t>
+          <t>00400A_調整方向</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_昨日</t>
+          <t>00400A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_今日</t>
+          <t>00400A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>00403A_權重_昨日</t>
+          <t>00400A_權重_昨日</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>00403A_權重_今日</t>
+          <t>00400A_權重_今日</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>00403A_權重變化</t>
+          <t>00400A_權重變化</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>00403A_股數_昨日</t>
+          <t>00400A_股數_昨日</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>00403A_股數_今日</t>
+          <t>00400A_股數_今日</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
-        <is>
-          <t>00403A_股數變化</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>00993A_異動類型</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>00993A_調整方向</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>00993A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>00993A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>00993A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>00993A_權重_今日</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>00993A_權重變化</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>00993A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>00993A_股數_今日</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>00993A_股數變化</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>00400A_異動類型</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>00400A_調整方向</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>00400A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>00400A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>00400A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>00400A_權重_今日</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>00400A_權重變化</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>00400A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>00400A_股數_今日</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
         <is>
           <t>00400A_股數變化</t>
         </is>
@@ -741,12 +641,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -754,7 +654,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00403A,00991A,00993A</t>
+          <t>00400A,00991A,00993A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -774,175 +674,133 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.04%</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>+2.04%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>9000</v>
+        <v>1400000</v>
       </c>
       <c r="W2" t="n">
-        <v>10400000</v>
+        <v>1000</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>10,391,000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+          <t>-1,399,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2.73%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2.66%</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>191000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>183000</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
+          <t>台 燿</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.20%</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>5.71%</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>+0.51%</t>
-        </is>
-      </c>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>3,000,000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1.66%</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1.74%</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>+0.08%</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1147000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1197000</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>50,000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
+        <v>175000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>南亞塑膠</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00400A,00991A,00993A</t>
+          <t>00400A,00991A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -957,46 +815,32 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>+0.08%</t>
-        </is>
-      </c>
+          <t>南亞塑膠</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>2.10%</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
-        <v>1400000</v>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-1,399,000</t>
-        </is>
-      </c>
+        <v>6700000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -1007,246 +851,172 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2.73%</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2.66%</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>191000</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>183000</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-8,000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>台 燿</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.89%</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="n">
-        <v>175000</v>
-      </c>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2.58%</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>1861000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3041000</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>1,180,000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00981A,00982A,00991A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+          <t>00991A,00993A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5.21%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>5.02%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.19%</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>6490561</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6332561</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-158,000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>聯華電子</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>聯華電子</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>+2.04%</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>10400000</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>10,391,000</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>緯穎科技</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>緯穎科技</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-0.30%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>3.26%</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>+3.56%</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>1500020</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1150020</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-350,000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>1171225</v>
+        <v>1147000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1136225</v>
+        <v>1197000</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr"/>
@@ -1259,36 +1029,16 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞塑膠</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1296,57 +1046,111 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00400A,00991A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>+0.18%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>5028000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6628000</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1,600,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>南亞塑膠</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2.10%</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>6700000</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>564000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>574000</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1357,72 +1161,16 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2.58%</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>+1.08%</t>
-        </is>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1861000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>3041000</v>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1,180,000</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1430,7 +1178,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
+          <t>00981A,00991A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1440,55 +1188,91 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>5.02%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5028000</v>
+        <v>6490561</v>
       </c>
       <c r="M6" t="n">
-        <v>6628000</v>
+        <v>6332561</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1,600,000</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+          <t>-158,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>+3.56%</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1500020</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1150020</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-350,000</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1509,62 +1293,6 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>1.30%</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1.31%</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>564000</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>574000</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/etf_holdings/2026-09-17_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-17_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR6"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,100 +539,200 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>00982A_異動類型</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>00982A_調整方向</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>00982A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>00982A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>00982A_權重變化</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>00982A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>00982A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>00982A_股數變化</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>00403A_異動類型</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>00403A_調整方向</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>00403A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>00403A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>00403A_權重變化</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>00403A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>00403A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>00403A_股數變化</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>00400A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00400A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00400A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00400A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00400A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00400A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00400A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00400A_股數變化</t>
         </is>
@@ -641,12 +741,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -654,7 +754,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00400A,00991A,00993A</t>
+          <t>00403A,00991A,00993A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -674,133 +774,175 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>+2.04%</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>10400000</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>10,391,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>5.20%</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>5.71%</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>+0.51%</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>3,000,000</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
           <t>+0.08%</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-1,399,000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2.73%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>2.66%</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>191000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>183000</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-8,000</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>台 燿</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.89%</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>175000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>1147000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1197000</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>南亞塑膠</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00400A,00991A</t>
+          <t>00400A,00991A,00993A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -815,32 +957,46 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>南亞塑膠</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>1400000</v>
+      </c>
       <c r="W3" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-1,399,000</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -851,82 +1007,156 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2.58%</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>+1.08%</t>
-        </is>
-      </c>
-      <c r="AP3" t="n">
-        <v>1861000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3041000</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>1,180,000</t>
-        </is>
-      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2.73%</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2.66%</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>191000</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>183000</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>台 燿</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="n">
+        <v>175000</v>
+      </c>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00991A,00993A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>00981A,00982A,00991A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5.21%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5.02%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>6490561</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6332561</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-158,000</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -934,43 +1164,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>緯穎科技</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>緯穎科技</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>+2.04%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9000</v>
+        <v>1500020</v>
       </c>
       <c r="W4" t="n">
-        <v>10400000</v>
+        <v>1150020</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>10,391,000</t>
+          <t>-350,000</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -980,43 +1210,43 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>1147000</v>
+        <v>1171225</v>
       </c>
       <c r="AG4" t="n">
-        <v>1197000</v>
+        <v>1136225</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr"/>
@@ -1029,16 +1259,36 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>南亞塑膠</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1046,111 +1296,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.42%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>+0.18%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>5028000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6628000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1,600,000</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+          <t>00400A,00991A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>南亞塑膠</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2.10%</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>6700000</v>
+      </c>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1.30%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>1.31%</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>564000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>574000</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1161,16 +1357,72 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2.58%</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1861000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3041000</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>1,180,000</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1178,7 +1430,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00981A,00991A</t>
+          <t>00981A,00993A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1188,91 +1440,55 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6490561</v>
+        <v>5028000</v>
       </c>
       <c r="M6" t="n">
-        <v>6332561</v>
+        <v>6628000</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-158,000</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>緯穎科技</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>緯穎科技</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-0.30%</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>3.26%</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>+3.56%</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>1500020</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1150020</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-350,000</t>
-        </is>
-      </c>
+          <t>1,600,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1293,6 +1509,62 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>564000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>574000</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
